--- a/ig/DM-MARS-2026/ASS-A20-RolePriseCharge-GenreActivite.xlsx
+++ b/ig/DM-MARS-2026/ASS-A20-RolePriseCharge-GenreActivite.xlsx
@@ -99,7 +99,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge|20260202120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge|20260330120000</t>
   </si>
   <si>
     <t/>
